--- a/exports/trend_1d/TORNTPHARM_full_report.xlsx
+++ b/exports/trend_1d/TORNTPHARM_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:U61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>12.05</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42061</v>
+        <v>42062</v>
       </c>
       <c r="H2" t="n">
-        <v>535.45</v>
+        <v>521.55</v>
       </c>
       <c r="I2" t="n">
         <v>532.78188744992</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.04</v>
+        <v>-6.53</v>
       </c>
       <c r="L2" t="n">
-        <v>5.03</v>
+        <v>7.7</v>
       </c>
       <c r="M2" t="n">
         <v>2.63</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>11.66</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42094</v>
+        <v>42095</v>
       </c>
       <c r="H3" t="n">
-        <v>579.3</v>
+        <v>597.75</v>
       </c>
       <c r="I3" t="n">
         <v>582.3539845706335</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K3" t="n">
-        <v>-11.07</v>
+        <v>-14.61</v>
       </c>
       <c r="L3" t="n">
-        <v>12.65</v>
+        <v>16.1</v>
       </c>
       <c r="M3" t="n">
         <v>3.35</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.06</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42114</v>
+        <v>42115</v>
       </c>
       <c r="H4" t="n">
-        <v>618</v>
+        <v>587.25</v>
       </c>
       <c r="I4" t="n">
         <v>593.4729452682113</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>3.39</v>
+        <v>-1.76</v>
       </c>
       <c r="L4" t="n">
         <v>2.64</v>
@@ -669,7 +716,7 @@
         <v>0.64</v>
       </c>
       <c r="N4" t="n">
-        <v>3.53</v>
+        <v>4.98</v>
       </c>
       <c r="O4" t="n">
         <v>3.18</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>15.95</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42172</v>
+        <v>42173</v>
       </c>
       <c r="H5" t="n">
-        <v>648.6</v>
+        <v>668.85</v>
       </c>
       <c r="I5" t="n">
         <v>664.0566504437077</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K5" t="n">
-        <v>-10.45</v>
+        <v>-13.9</v>
       </c>
       <c r="L5" t="n">
-        <v>12.79</v>
+        <v>16.52</v>
       </c>
       <c r="M5" t="n">
         <v>5.79</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>8.890000000000001</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H6" t="n">
-        <v>820.7</v>
+        <v>737.55</v>
       </c>
       <c r="I6" t="n">
         <v>744.942160591762</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K6" t="n">
-        <v>22.7</v>
+        <v>10.27</v>
       </c>
       <c r="L6" t="n">
         <v>4.54</v>
       </c>
       <c r="M6" t="n">
-        <v>0.53</v>
+        <v>3.13</v>
       </c>
       <c r="N6" t="n">
-        <v>3.43</v>
+        <v>10.13</v>
       </c>
       <c r="O6" t="n">
         <v>3.12</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>17.13</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42278</v>
+        <v>42282</v>
       </c>
       <c r="H7" t="n">
-        <v>746.3</v>
+        <v>788.85</v>
       </c>
       <c r="I7" t="n">
         <v>788.2157921664533</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.19</v>
+        <v>-6.96</v>
       </c>
       <c r="L7" t="n">
         <v>16.49</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>14.59</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42335</v>
+        <v>42338</v>
       </c>
       <c r="H8" t="n">
-        <v>761.2</v>
+        <v>712.75</v>
       </c>
       <c r="I8" t="n">
         <v>726.6373415358859</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.51</v>
+        <v>-9.65</v>
       </c>
       <c r="L8" t="n">
-        <v>4.86</v>
+        <v>11.04</v>
       </c>
       <c r="M8" t="n">
         <v>2.3</v>
       </c>
       <c r="N8" t="n">
-        <v>2.41</v>
+        <v>6.36</v>
       </c>
       <c r="O8" t="n">
         <v>5.7</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>12.53</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42450</v>
+        <v>42451</v>
       </c>
       <c r="H9" t="n">
-        <v>673.85</v>
+        <v>709.05</v>
       </c>
       <c r="I9" t="n">
         <v>683.6210868576404</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K9" t="n">
-        <v>5.46</v>
+        <v>0.52</v>
       </c>
       <c r="L9" t="n">
         <v>8.16</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.99</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42509</v>
+        <v>42510</v>
       </c>
       <c r="H10" t="n">
-        <v>687.35</v>
+        <v>662.5</v>
       </c>
       <c r="I10" t="n">
         <v>672.879557393648</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.06</v>
+        <v>-6.57</v>
       </c>
       <c r="L10" t="n">
         <v>8.039999999999999</v>
@@ -1011,7 +1130,7 @@
         <v>0.71</v>
       </c>
       <c r="N10" t="n">
-        <v>3.33</v>
+        <v>3.62</v>
       </c>
       <c r="O10" t="n">
         <v>5.22</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>9.48</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42558</v>
+        <v>42559</v>
       </c>
       <c r="H11" t="n">
-        <v>699.15</v>
+        <v>710.15</v>
       </c>
       <c r="I11" t="n">
         <v>706.8462249776603</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.53</v>
+        <v>-7.19</v>
       </c>
       <c r="L11" t="n">
-        <v>7.17</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="M11" t="n">
         <v>1.13</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>6.02</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42669</v>
+        <v>42670</v>
       </c>
       <c r="H12" t="n">
-        <v>783.4</v>
+        <v>712.85</v>
       </c>
       <c r="I12" t="n">
         <v>765.9134672189595</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K12" t="n">
-        <v>10.31</v>
+        <v>0.38</v>
       </c>
       <c r="L12" t="n">
         <v>4.03</v>
       </c>
       <c r="M12" t="n">
-        <v>2.23</v>
+        <v>5.54</v>
       </c>
       <c r="N12" t="n">
-        <v>5.22</v>
+        <v>9.01</v>
       </c>
       <c r="O12" t="n">
         <v>1.57</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>12.67</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42789</v>
+        <v>42793</v>
       </c>
       <c r="H13" t="n">
-        <v>648.3</v>
+        <v>671.75</v>
       </c>
       <c r="I13" t="n">
         <v>663.121185564478</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K13" t="n">
-        <v>9.06</v>
+        <v>5.77</v>
       </c>
       <c r="L13" t="n">
         <v>4.86</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>9.279999999999999</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42857</v>
+        <v>42858</v>
       </c>
       <c r="H14" t="n">
-        <v>694.4</v>
+        <v>671.8</v>
       </c>
       <c r="I14" t="n">
         <v>693.3788523039253</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K14" t="n">
-        <v>3.37</v>
+        <v>0.01</v>
       </c>
       <c r="L14" t="n">
         <v>3.46</v>
@@ -1239,7 +1406,7 @@
         <v>0.88</v>
       </c>
       <c r="N14" t="n">
-        <v>3.07</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
         <v>3.62</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>10.91</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42920</v>
+        <v>42921</v>
       </c>
       <c r="H15" t="n">
-        <v>620.3</v>
+        <v>636.7</v>
       </c>
       <c r="I15" t="n">
         <v>632.0426316270524</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K15" t="n">
-        <v>7.67</v>
+        <v>5.22</v>
       </c>
       <c r="L15" t="n">
         <v>3.06</v>
@@ -1296,7 +1475,7 @@
         <v>1.13</v>
       </c>
       <c r="N15" t="n">
-        <v>2.47</v>
+        <v>2.64</v>
       </c>
       <c r="O15" t="n">
         <v>-3.25</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43046</v>
+        <v>43047</v>
       </c>
       <c r="H16" t="n">
-        <v>634.4</v>
+        <v>620.2</v>
       </c>
       <c r="I16" t="n">
         <v>623.8739395937673</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.36</v>
+        <v>-2.59</v>
       </c>
       <c r="L16" t="n">
         <v>9.9</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>14.6</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43084</v>
+        <v>43087</v>
       </c>
       <c r="H17" t="n">
-        <v>672.4</v>
+        <v>679.6</v>
       </c>
       <c r="I17" t="n">
         <v>678.1703950296185</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K17" t="n">
-        <v>-8.42</v>
+        <v>-9.58</v>
       </c>
       <c r="L17" t="n">
-        <v>9.4</v>
+        <v>10.83</v>
       </c>
       <c r="M17" t="n">
         <v>0.99</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,25 +1661,25 @@
         <v>7.75</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43136</v>
+        <v>43137</v>
       </c>
       <c r="H18" t="n">
-        <v>671.15</v>
+        <v>666.85</v>
       </c>
       <c r="I18" t="n">
         <v>669.9788958405869</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.24</v>
+        <v>-1.88</v>
       </c>
       <c r="L18" t="n">
-        <v>2.88</v>
+        <v>6.45</v>
       </c>
       <c r="M18" t="n">
-        <v>2.82</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
         <v>3.03</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>8.32</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43207</v>
+        <v>43208</v>
       </c>
       <c r="H19" t="n">
-        <v>669.35</v>
+        <v>676.75</v>
       </c>
       <c r="I19" t="n">
         <v>673.815063890125</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.37</v>
+        <v>-1.48</v>
       </c>
       <c r="L19" t="n">
         <v>8.720000000000001</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>7.8</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43244</v>
+        <v>43245</v>
       </c>
       <c r="H20" t="n">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="I20" t="n">
         <v>659.6812912522082</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.48</v>
+        <v>-2.62</v>
       </c>
       <c r="L20" t="n">
         <v>3.69</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>9.949999999999999</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43251</v>
+        <v>43252</v>
       </c>
       <c r="H21" t="n">
-        <v>705.75</v>
+        <v>727.45</v>
       </c>
       <c r="I21" t="n">
         <v>724.5492208694266</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K21" t="n">
-        <v>-7.09</v>
+        <v>-10.39</v>
       </c>
       <c r="L21" t="n">
-        <v>8.449999999999999</v>
+        <v>12.88</v>
       </c>
       <c r="M21" t="n">
         <v>0.52</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>11.37</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43364</v>
+        <v>43367</v>
       </c>
       <c r="H22" t="n">
-        <v>864.85</v>
+        <v>841.65</v>
       </c>
       <c r="I22" t="n">
         <v>850.0882945873309</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K22" t="n">
-        <v>18.89</v>
+        <v>15.7</v>
       </c>
       <c r="L22" t="n">
         <v>5.76</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>14.34</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43433</v>
+        <v>43434</v>
       </c>
       <c r="H23" t="n">
-        <v>857.3</v>
+        <v>886.9</v>
       </c>
       <c r="I23" t="n">
         <v>872.7331729327749</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.86</v>
+        <v>-5.38</v>
       </c>
       <c r="L23" t="n">
-        <v>3.85</v>
+        <v>5.74</v>
       </c>
       <c r="M23" t="n">
         <v>1.62</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>10.98</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43496</v>
+        <v>43497</v>
       </c>
       <c r="H24" t="n">
-        <v>909.4</v>
+        <v>899.35</v>
       </c>
       <c r="I24" t="n">
         <v>900.8844354678625</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K24" t="n">
-        <v>2.54</v>
+        <v>1.4</v>
       </c>
       <c r="L24" t="n">
         <v>6.12</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43549</v>
+        <v>43550</v>
       </c>
       <c r="H25" t="n">
-        <v>933.15</v>
+        <v>941.95</v>
       </c>
       <c r="I25" t="n">
         <v>934.9869469761624</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.76</v>
+        <v>-4.74</v>
       </c>
       <c r="L25" t="n">
-        <v>4.8</v>
+        <v>5.49</v>
       </c>
       <c r="M25" t="n">
         <v>0.86</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>6.11</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43560</v>
+        <v>43563</v>
       </c>
       <c r="H26" t="n">
-        <v>920.8</v>
+        <v>897.45</v>
       </c>
       <c r="I26" t="n">
         <v>915.400953067676</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.25</v>
+        <v>-4.72</v>
       </c>
       <c r="L26" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="M26" t="n">
         <v>0.2</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43670</v>
+        <v>43671</v>
       </c>
       <c r="H27" t="n">
-        <v>803.5</v>
+        <v>812.1</v>
       </c>
       <c r="I27" t="n">
         <v>806.7829958303762</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K27" t="n">
-        <v>10.47</v>
+        <v>9.51</v>
       </c>
       <c r="L27" t="n">
         <v>4.41</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>12.39</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43739</v>
+        <v>43741</v>
       </c>
       <c r="H28" t="n">
-        <v>808.1</v>
+        <v>799.4</v>
       </c>
       <c r="I28" t="n">
         <v>801.1955986902584</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.49</v>
+        <v>-1.56</v>
       </c>
       <c r="L28" t="n">
         <v>3.19</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43761</v>
+        <v>43762</v>
       </c>
       <c r="H29" t="n">
-        <v>840.1</v>
+        <v>883.85</v>
       </c>
       <c r="I29" t="n">
         <v>865.1127020687552</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K29" t="n">
-        <v>-5.09</v>
+        <v>-10.56</v>
       </c>
       <c r="L29" t="n">
-        <v>8.949999999999999</v>
+        <v>11.46</v>
       </c>
       <c r="M29" t="n">
         <v>0.62</v>
       </c>
       <c r="N29" t="n">
-        <v>3.26</v>
+        <v>5.21</v>
       </c>
       <c r="O29" t="n">
         <v>-1.08</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>12.24</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43901</v>
+        <v>43902</v>
       </c>
       <c r="H30" t="n">
-        <v>1069.45</v>
+        <v>993.95</v>
       </c>
       <c r="I30" t="n">
         <v>1031.579399316475</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K30" t="n">
-        <v>21</v>
+        <v>12.46</v>
       </c>
       <c r="L30" t="n">
         <v>4.54</v>
       </c>
       <c r="M30" t="n">
-        <v>1.34</v>
+        <v>2.05</v>
       </c>
       <c r="N30" t="n">
-        <v>5.46</v>
+        <v>7.06</v>
       </c>
       <c r="O30" t="n">
         <v>5.21</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>6</v>
+      </c>
+      <c r="U30" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>16.87</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43924</v>
+        <v>43928</v>
       </c>
       <c r="H31" t="n">
-        <v>1038.5</v>
+        <v>1177.15</v>
       </c>
       <c r="I31" t="n">
         <v>1065.046377420771</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.48</v>
+        <v>-18.43</v>
       </c>
       <c r="L31" t="n">
-        <v>7.69</v>
+        <v>20.15</v>
       </c>
       <c r="M31" t="n">
-        <v>2.42</v>
+        <v>3.98</v>
       </c>
       <c r="N31" t="n">
-        <v>6.87</v>
+        <v>13.35</v>
       </c>
       <c r="O31" t="n">
         <v>-7.06</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>23.17</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43984</v>
+        <v>43985</v>
       </c>
       <c r="H32" t="n">
-        <v>1184.7</v>
+        <v>1153.85</v>
       </c>
       <c r="I32" t="n">
         <v>1159.912709387763</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K32" t="n">
-        <v>0.64</v>
+        <v>-1.98</v>
       </c>
       <c r="L32" t="n">
         <v>10.28</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>15.58</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44042</v>
+        <v>44043</v>
       </c>
       <c r="H33" t="n">
-        <v>1218.8</v>
+        <v>1331.8</v>
       </c>
       <c r="I33" t="n">
         <v>1244.311613327705</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K33" t="n">
-        <v>-5.63</v>
+        <v>-15.42</v>
       </c>
       <c r="L33" t="n">
-        <v>13.32</v>
+        <v>19.4</v>
       </c>
       <c r="M33" t="n">
-        <v>1.68</v>
+        <v>2.56</v>
       </c>
       <c r="N33" t="n">
-        <v>4.01</v>
+        <v>9.27</v>
       </c>
       <c r="O33" t="n">
         <v>-2.6</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>12.2</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44071</v>
+        <v>44074</v>
       </c>
       <c r="H34" t="n">
-        <v>1354.7</v>
+        <v>1330.8</v>
       </c>
       <c r="I34" t="n">
         <v>1345.675246109834</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K34" t="n">
-        <v>1.72</v>
+        <v>-0.08</v>
       </c>
       <c r="L34" t="n">
         <v>6.14</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>9.65</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44179</v>
+        <v>44180</v>
       </c>
       <c r="H35" t="n">
-        <v>1351.9</v>
+        <v>1374.6</v>
       </c>
       <c r="I35" t="n">
         <v>1369.63467675445</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K35" t="n">
-        <v>-1.59</v>
+        <v>-3.29</v>
       </c>
       <c r="L35" t="n">
         <v>10.63</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,25 +2903,25 @@
         <v>7.69</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44211</v>
+        <v>44214</v>
       </c>
       <c r="H36" t="n">
-        <v>1355.85</v>
+        <v>1322.55</v>
       </c>
       <c r="I36" t="n">
         <v>1327.584098581044</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K36" t="n">
-        <v>-1.36</v>
+        <v>-3.79</v>
       </c>
       <c r="L36" t="n">
         <v>6.03</v>
       </c>
       <c r="M36" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="N36" t="n">
         <v>4</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>9.25</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44292</v>
+        <v>44293</v>
       </c>
       <c r="H37" t="n">
-        <v>1281.45</v>
+        <v>1288.55</v>
       </c>
       <c r="I37" t="n">
         <v>1284.836993399129</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K37" t="n">
-        <v>3.11</v>
+        <v>2.57</v>
       </c>
       <c r="L37" t="n">
         <v>5.97</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>6.8</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44494</v>
+        <v>44495</v>
       </c>
       <c r="H38" t="n">
-        <v>1542</v>
+        <v>1472.1</v>
       </c>
       <c r="I38" t="n">
         <v>1474.31030033126</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K38" t="n">
-        <v>19.67</v>
+        <v>14.24</v>
       </c>
       <c r="L38" t="n">
         <v>3.94</v>
@@ -2607,7 +3062,7 @@
         <v>1.38</v>
       </c>
       <c r="N38" t="n">
-        <v>4.12</v>
+        <v>4.53</v>
       </c>
       <c r="O38" t="n">
         <v>0.55</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>137</v>
+        <v>138</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>7</v>
+      </c>
+      <c r="U38" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>14.34</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H39" t="n">
-        <v>1495.25</v>
+        <v>1518.05</v>
       </c>
       <c r="I39" t="n">
         <v>1510.170693881888</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.57</v>
+        <v>-3.12</v>
       </c>
       <c r="L39" t="n">
         <v>5.79</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>10.66</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44586</v>
+        <v>44588</v>
       </c>
       <c r="H40" t="n">
-        <v>1580.5</v>
+        <v>1341.75</v>
       </c>
       <c r="I40" t="n">
         <v>1501.685593015861</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K40" t="n">
-        <v>4.11</v>
+        <v>-11.61</v>
       </c>
       <c r="L40" t="n">
-        <v>3.67</v>
+        <v>13.18</v>
       </c>
       <c r="M40" t="n">
-        <v>0.97</v>
+        <v>6.99</v>
       </c>
       <c r="N40" t="n">
-        <v>3.68</v>
+        <v>15.11</v>
       </c>
       <c r="O40" t="n">
         <v>1.52</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>17.8</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44630</v>
+        <v>44631</v>
       </c>
       <c r="H41" t="n">
-        <v>1384.6</v>
+        <v>1411.6</v>
       </c>
       <c r="I41" t="n">
         <v>1403.936462394294</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.19</v>
+        <v>-5.21</v>
       </c>
       <c r="L41" t="n">
         <v>9.56</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>10.07</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H42" t="n">
-        <v>1341.7</v>
+        <v>1325.4</v>
       </c>
       <c r="I42" t="n">
         <v>1327.504564184663</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K42" t="n">
-        <v>-4.95</v>
+        <v>-6.11</v>
       </c>
       <c r="L42" t="n">
-        <v>5.75</v>
+        <v>6.68</v>
       </c>
       <c r="M42" t="n">
         <v>1.3</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>8.890000000000001</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44706</v>
+        <v>44707</v>
       </c>
       <c r="H43" t="n">
-        <v>1317.4</v>
+        <v>1450.45</v>
       </c>
       <c r="I43" t="n">
         <v>1374.32898969924</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K43" t="n">
-        <v>0.6</v>
+        <v>-9.43</v>
       </c>
       <c r="L43" t="n">
-        <v>2.72</v>
+        <v>10.57</v>
       </c>
       <c r="M43" t="n">
-        <v>1.17</v>
+        <v>4.41</v>
       </c>
       <c r="N43" t="n">
-        <v>3.12</v>
+        <v>10.1</v>
       </c>
       <c r="O43" t="n">
         <v>-1.21</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>12.77</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44914</v>
+        <v>44915</v>
       </c>
       <c r="H44" t="n">
-        <v>1597.85</v>
+        <v>1575.2</v>
       </c>
       <c r="I44" t="n">
         <v>1583.84654800439</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K44" t="n">
-        <v>10.16</v>
+        <v>8.6</v>
       </c>
       <c r="L44" t="n">
         <v>6.29</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>142</v>
+        <v>143</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>7</v>
+      </c>
+      <c r="U44" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>5.92</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45000</v>
+        <v>45001</v>
       </c>
       <c r="H45" t="n">
-        <v>1540.05</v>
+        <v>1551.65</v>
       </c>
       <c r="I45" t="n">
         <v>1547.895149761659</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K45" t="n">
-        <v>2.23</v>
+        <v>1.5</v>
       </c>
       <c r="L45" t="n">
         <v>3.63</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>6.03</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45168</v>
+        <v>45169</v>
       </c>
       <c r="H46" t="n">
-        <v>1954.7</v>
+        <v>1842.5</v>
       </c>
       <c r="I46" t="n">
         <v>1919.754017628991</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K46" t="n">
-        <v>25.98</v>
+        <v>18.74</v>
       </c>
       <c r="L46" t="n">
         <v>3.24</v>
@@ -3063,7 +3614,7 @@
         <v>4.08</v>
       </c>
       <c r="N46" t="n">
-        <v>3.32</v>
+        <v>5.74</v>
       </c>
       <c r="O46" t="n">
         <v>0.75</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>6</v>
+      </c>
+      <c r="U46" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>10.83</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45232</v>
+        <v>45233</v>
       </c>
       <c r="H47" t="n">
-        <v>1927.4</v>
+        <v>1960.4</v>
       </c>
       <c r="I47" t="n">
         <v>1948.937058289747</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K47" t="n">
-        <v>-4.61</v>
+        <v>-6.4</v>
       </c>
       <c r="L47" t="n">
-        <v>6.09</v>
+        <v>6.81</v>
       </c>
       <c r="M47" t="n">
         <v>1.69</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>7.07</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45369</v>
+        <v>45370</v>
       </c>
       <c r="H48" t="n">
-        <v>2569.65</v>
+        <v>2501.5</v>
       </c>
       <c r="I48" t="n">
         <v>2535.747168137617</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K48" t="n">
-        <v>31.08</v>
+        <v>27.6</v>
       </c>
       <c r="L48" t="n">
         <v>1.42</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>5</v>
+      </c>
+      <c r="U48" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>9.960000000000001</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="H49" t="n">
-        <v>2670</v>
+        <v>2734.7</v>
       </c>
       <c r="I49" t="n">
         <v>2716.136208489173</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K49" t="n">
-        <v>-6.74</v>
+        <v>-9.32</v>
       </c>
       <c r="L49" t="n">
-        <v>9.1</v>
+        <v>11.25</v>
       </c>
       <c r="M49" t="n">
         <v>0.92</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>7.1</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="H50" t="n">
-        <v>2587.55</v>
+        <v>2524.35</v>
       </c>
       <c r="I50" t="n">
         <v>2541.583073040925</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K50" t="n">
-        <v>-5.38</v>
+        <v>-7.69</v>
       </c>
       <c r="L50" t="n">
-        <v>5.84</v>
+        <v>7.85</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45447</v>
+        <v>45448</v>
       </c>
       <c r="H51" t="n">
-        <v>2694</v>
+        <v>2780.4</v>
       </c>
       <c r="I51" t="n">
         <v>2773.189264753165</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K51" t="n">
-        <v>-6.72</v>
+        <v>-10.14</v>
       </c>
       <c r="L51" t="n">
-        <v>10.72</v>
+        <v>10.95</v>
       </c>
       <c r="M51" t="n">
         <v>6.98</v>
       </c>
       <c r="N51" t="n">
-        <v>2.99</v>
+        <v>3.21</v>
       </c>
       <c r="O51" t="n">
         <v>-2.44</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>10.26</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45593</v>
+        <v>45594</v>
       </c>
       <c r="H52" t="n">
-        <v>3316.7</v>
+        <v>3215.65</v>
       </c>
       <c r="I52" t="n">
         <v>3280.586964945427</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K52" t="n">
-        <v>19.29</v>
+        <v>15.65</v>
       </c>
       <c r="L52" t="n">
         <v>3.24</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>5</v>
+      </c>
+      <c r="U52" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>10.59</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45625</v>
+        <v>45628</v>
       </c>
       <c r="H53" t="n">
-        <v>3324.2</v>
+        <v>3339.15</v>
       </c>
       <c r="I53" t="n">
         <v>3333.794389823825</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.38</v>
+        <v>-3.84</v>
       </c>
       <c r="L53" t="n">
-        <v>3.65</v>
+        <v>5.53</v>
       </c>
       <c r="M53" t="n">
         <v>1.23</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,25 +4145,25 @@
         <v>7.38</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="H54" t="n">
-        <v>3274.45</v>
+        <v>3235.35</v>
       </c>
       <c r="I54" t="n">
         <v>3236.196718006645</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.94</v>
+        <v>-3.11</v>
       </c>
       <c r="L54" t="n">
-        <v>2.25</v>
+        <v>3.29</v>
       </c>
       <c r="M54" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="N54" t="n">
         <v>2.33</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,25 +4214,25 @@
         <v>7.98</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45735</v>
+        <v>45736</v>
       </c>
       <c r="H55" t="n">
-        <v>3191.3</v>
+        <v>3230.75</v>
       </c>
       <c r="I55" t="n">
         <v>3214.031564967361</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K55" t="n">
-        <v>1.36</v>
+        <v>0.14</v>
       </c>
       <c r="L55" t="n">
         <v>4.89</v>
       </c>
       <c r="M55" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="N55" t="n">
         <v>3.08</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45874</v>
+        <v>45875</v>
       </c>
       <c r="H56" t="n">
-        <v>3589.2</v>
+        <v>3524.1</v>
       </c>
       <c r="I56" t="n">
         <v>3527.566069755249</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K56" t="n">
-        <v>11.09</v>
+        <v>9.08</v>
       </c>
       <c r="L56" t="n">
         <v>4</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>6</v>
+      </c>
+      <c r="U56" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>7.16</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="H57" t="n">
-        <v>3580</v>
+        <v>3817.5</v>
       </c>
       <c r="I57" t="n">
         <v>3708.213342410941</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.59</v>
+        <v>-8.33</v>
       </c>
       <c r="L57" t="n">
-        <v>4.99</v>
+        <v>8.82</v>
       </c>
       <c r="M57" t="n">
-        <v>0.92</v>
+        <v>2.23</v>
       </c>
       <c r="N57" t="n">
-        <v>2.06</v>
+        <v>6.63</v>
       </c>
       <c r="O57" t="n">
         <v>-1.81</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>4</v>
+      </c>
+      <c r="U57" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>9.16</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="H58" t="n">
-        <v>4220.2</v>
+        <v>4111.3</v>
       </c>
       <c r="I58" t="n">
         <v>4143.241736561072</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K58" t="n">
-        <v>10.55</v>
+        <v>7.7</v>
       </c>
       <c r="L58" t="n">
         <v>5.65</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>6</v>
+      </c>
+      <c r="U58" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>11.04</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="H59" t="n">
-        <v>4362.7</v>
+        <v>4380.8</v>
       </c>
       <c r="I59" t="n">
         <v>4368.772750361853</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K59" t="n">
-        <v>-6.11</v>
+        <v>-6.56</v>
       </c>
       <c r="L59" t="n">
         <v>7.92</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>6.58</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H60" t="n">
-        <v>4716.2</v>
+        <v>4617.1</v>
       </c>
       <c r="I60" t="n">
         <v>4705.973424941807</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K60" t="n">
-        <v>7.66</v>
+        <v>5.39</v>
       </c>
       <c r="L60" t="n">
         <v>3.21</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>6</v>
+      </c>
+      <c r="U60" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="61">
@@ -3921,6 +4652,14 @@
       <c r="Q61" t="n">
         <v>14</v>
       </c>
+      <c r="R61" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8879,7 +9618,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>71.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -8889,7 +9628,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -8899,7 +9638,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8">
@@ -8909,7 +9648,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -8919,7 +9658,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10">
@@ -8929,7 +9668,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>139.2</v>
+        <v>140.4</v>
       </c>
     </row>
     <row r="11">
@@ -8939,7 +9678,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -8949,7 +9688,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
@@ -8959,7 +9698,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16.9</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="14">
@@ -8969,7 +9708,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.25</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="15">
@@ -8979,7 +9718,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.44</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="16">
@@ -8989,7 +9728,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-2.09</v>
+        <v>-5.48</v>
       </c>
     </row>
     <row r="17">
@@ -8999,7 +9738,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31.08</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="18">
@@ -9009,7 +9748,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>44.1</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="19">
@@ -9019,7 +9758,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.15</v>
+        <v>7.57</v>
       </c>
     </row>
     <row r="20">
@@ -9029,7 +9768,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.65</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="21">
@@ -9039,7 +9778,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.49</v>
+        <v>20.15</v>
       </c>
     </row>
     <row r="22">
@@ -9049,7 +9788,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
@@ -9059,7 +9798,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -9069,7 +9808,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.68</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="25">
@@ -9079,7 +9818,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.98</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="26">
@@ -9089,7 +9828,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.98</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="27">
@@ -9099,7 +9838,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.48</v>
+        <v>15.11</v>
       </c>
     </row>
     <row r="28">
@@ -9109,7 +9848,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29">
